--- a/data/data.xlsx
+++ b/data/data.xlsx
@@ -5,11 +5,11 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rayvi\OneDrive\AUTOMATION\Playwright\orangehrm-automation\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rayvi\OneDrive\AUTOMATION\Playwright\pw_orangehrm-automation\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="10044" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="10044" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Login" sheetId="1" r:id="rId1"/>
@@ -67,7 +67,7 @@
     <t>searchName</t>
   </si>
   <si>
-    <t>fi</t>
+    <t xml:space="preserve">firstName </t>
   </si>
 </sst>
 </file>
@@ -488,6 +488,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:A2"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4"/>
+  <cols>
+    <col min="1" max="1" width="28.44140625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" t="s">

--- a/data/data.xlsx
+++ b/data/data.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="10044" activeTab="2"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="10044" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Login" sheetId="1" r:id="rId1"/>
@@ -475,7 +475,7 @@
         <v>10</v>
       </c>
       <c r="D2">
-        <v>9991</v>
+        <v>9990</v>
       </c>
     </row>
   </sheetData>
